--- a/test/004_UT-権限管理テスト/権限管理テスト証跡.xlsx
+++ b/test/004_UT-権限管理テスト/権限管理テスト証跡.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="テスト証跡" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="スクリーンショット証跡" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +54,14 @@
       <color rgb="00333333"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -81,8 +88,18 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3A72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F2F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -104,11 +121,69 @@
         <color rgb="FFB0B8C4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB0B8C4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB0B8C4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B8C4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB0B8C4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B8C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB0B8C4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B8C4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B8C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -137,6 +212,21 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -211,6 +301,436 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>159</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>190</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>221</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>252</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>283</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>314</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>345</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>376</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>407</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>438</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>469</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>500</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -577,6 +1097,12 @@
           <t>【 ログイン・ロール表示確認（001〜006）】</t>
         </is>
       </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -806,6 +1332,12 @@
           <t>【 管理者権限確認（007〜010）】</t>
         </is>
       </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="11" t="n"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -961,6 +1493,12 @@
           <t>【 ユーザー管理画面確認（011〜013）】</t>
         </is>
       </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="11" t="n"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -1079,6 +1617,12 @@
           <t>【 API 権限制御確認（014〜017）】</t>
         </is>
       </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="11" t="n"/>
     </row>
     <row r="22" ht="56" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -1240,4 +1784,2184 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B528"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="116" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>権限管理テスト　スクリーンショット証跡</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>テストID：UT-AUTH-001 〜 UT-AUTH-017　　テスト実施日：2026/05/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-001</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>login.html　ログイン画面表示確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+    </row>
+    <row r="6" ht="14" customHeight="1">
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="16" t="n"/>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="16" t="n"/>
+    </row>
+    <row r="8" ht="14" customHeight="1">
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="16" t="n"/>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="16" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="16" t="n"/>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="14" customHeight="1">
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
+    </row>
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="16" t="n"/>
+    </row>
+    <row r="19" ht="14" customHeight="1">
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="14" customHeight="1">
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
+    </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="n"/>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="16" t="n"/>
+    </row>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="16" t="n"/>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="16" t="n"/>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="16" t="n"/>
+    </row>
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="16" t="n"/>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="16" t="n"/>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="16" t="n"/>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="16" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="16" t="n"/>
+    </row>
+    <row r="33" ht="10" customHeight="1"/>
+    <row r="34" ht="10" customHeight="1"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-002</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>staff1 ログイン → ダッシュボード遷移・ロール「一般担当」表示確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="16" t="n"/>
+    </row>
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="16" t="n"/>
+    </row>
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="16" t="n"/>
+      <c r="B38" s="16" t="n"/>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="16" t="n"/>
+      <c r="B39" s="16" t="n"/>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="16" t="n"/>
+      <c r="B40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="16" t="n"/>
+      <c r="B41" s="16" t="n"/>
+    </row>
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="16" t="n"/>
+      <c r="B42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="16" t="n"/>
+      <c r="B43" s="16" t="n"/>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="16" t="n"/>
+      <c r="B44" s="16" t="n"/>
+    </row>
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="16" t="n"/>
+      <c r="B45" s="16" t="n"/>
+    </row>
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="16" t="n"/>
+      <c r="B46" s="16" t="n"/>
+    </row>
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="16" t="n"/>
+      <c r="B47" s="16" t="n"/>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="16" t="n"/>
+      <c r="B48" s="16" t="n"/>
+    </row>
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="16" t="n"/>
+      <c r="B49" s="16" t="n"/>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="16" t="n"/>
+      <c r="B50" s="16" t="n"/>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="16" t="n"/>
+      <c r="B51" s="16" t="n"/>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="16" t="n"/>
+      <c r="B52" s="16" t="n"/>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="16" t="n"/>
+      <c r="B53" s="16" t="n"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="16" t="n"/>
+      <c r="B54" s="16" t="n"/>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="16" t="n"/>
+      <c r="B55" s="16" t="n"/>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="16" t="n"/>
+      <c r="B56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="16" t="n"/>
+      <c r="B57" s="16" t="n"/>
+    </row>
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="16" t="n"/>
+      <c r="B58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="16" t="n"/>
+      <c r="B59" s="16" t="n"/>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="16" t="n"/>
+      <c r="B60" s="16" t="n"/>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="16" t="n"/>
+      <c r="B61" s="16" t="n"/>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="16" t="n"/>
+      <c r="B62" s="16" t="n"/>
+    </row>
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="16" t="n"/>
+      <c r="B63" s="16" t="n"/>
+    </row>
+    <row r="64" ht="10" customHeight="1"/>
+    <row r="65" ht="10" customHeight="1"/>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-003</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>保険金支払状況ボタン グレーアウト・他3ボタン活性確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="16" t="n"/>
+      <c r="B67" s="16" t="n"/>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="16" t="n"/>
+      <c r="B68" s="16" t="n"/>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="16" t="n"/>
+      <c r="B69" s="16" t="n"/>
+    </row>
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="16" t="n"/>
+      <c r="B70" s="16" t="n"/>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="16" t="n"/>
+      <c r="B71" s="16" t="n"/>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="16" t="n"/>
+      <c r="B72" s="16" t="n"/>
+    </row>
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="16" t="n"/>
+      <c r="B73" s="16" t="n"/>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="16" t="n"/>
+      <c r="B74" s="16" t="n"/>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="16" t="n"/>
+      <c r="B75" s="16" t="n"/>
+    </row>
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="16" t="n"/>
+      <c r="B76" s="16" t="n"/>
+    </row>
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="16" t="n"/>
+      <c r="B77" s="16" t="n"/>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="16" t="n"/>
+      <c r="B78" s="16" t="n"/>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="16" t="n"/>
+      <c r="B79" s="16" t="n"/>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="16" t="n"/>
+      <c r="B80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="16" t="n"/>
+      <c r="B81" s="16" t="n"/>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="16" t="n"/>
+      <c r="B82" s="16" t="n"/>
+    </row>
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="16" t="n"/>
+      <c r="B83" s="16" t="n"/>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="16" t="n"/>
+      <c r="B84" s="16" t="n"/>
+    </row>
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="16" t="n"/>
+      <c r="B85" s="16" t="n"/>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="16" t="n"/>
+      <c r="B86" s="16" t="n"/>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="16" t="n"/>
+      <c r="B87" s="16" t="n"/>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="16" t="n"/>
+      <c r="B88" s="16" t="n"/>
+    </row>
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="16" t="n"/>
+      <c r="B89" s="16" t="n"/>
+    </row>
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="16" t="n"/>
+      <c r="B90" s="16" t="n"/>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="16" t="n"/>
+      <c r="B91" s="16" t="n"/>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="16" t="n"/>
+      <c r="B92" s="16" t="n"/>
+    </row>
+    <row r="93" ht="14" customHeight="1">
+      <c r="A93" s="16" t="n"/>
+      <c r="B93" s="16" t="n"/>
+    </row>
+    <row r="94" ht="14" customHeight="1">
+      <c r="A94" s="16" t="n"/>
+      <c r="B94" s="16" t="n"/>
+    </row>
+    <row r="95" ht="10" customHeight="1"/>
+    <row r="96" ht="10" customHeight="1"/>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-004</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>グレーアウトボタン ホバー時「権限がありません」ツールチップ確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="16" t="n"/>
+      <c r="B98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="16" t="n"/>
+      <c r="B99" s="16" t="n"/>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="16" t="n"/>
+      <c r="B100" s="16" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="16" t="n"/>
+      <c r="B101" s="16" t="n"/>
+    </row>
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="16" t="n"/>
+      <c r="B102" s="16" t="n"/>
+    </row>
+    <row r="103" ht="14" customHeight="1">
+      <c r="A103" s="16" t="n"/>
+      <c r="B103" s="16" t="n"/>
+    </row>
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="16" t="n"/>
+      <c r="B104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="16" t="n"/>
+      <c r="B105" s="16" t="n"/>
+    </row>
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="16" t="n"/>
+      <c r="B106" s="16" t="n"/>
+    </row>
+    <row r="107" ht="14" customHeight="1">
+      <c r="A107" s="16" t="n"/>
+      <c r="B107" s="16" t="n"/>
+    </row>
+    <row r="108" ht="14" customHeight="1">
+      <c r="A108" s="16" t="n"/>
+      <c r="B108" s="16" t="n"/>
+    </row>
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="16" t="n"/>
+      <c r="B109" s="16" t="n"/>
+    </row>
+    <row r="110" ht="14" customHeight="1">
+      <c r="A110" s="16" t="n"/>
+      <c r="B110" s="16" t="n"/>
+    </row>
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="16" t="n"/>
+      <c r="B111" s="16" t="n"/>
+    </row>
+    <row r="112" ht="14" customHeight="1">
+      <c r="A112" s="16" t="n"/>
+      <c r="B112" s="16" t="n"/>
+    </row>
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="16" t="n"/>
+      <c r="B113" s="16" t="n"/>
+    </row>
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="16" t="n"/>
+      <c r="B114" s="16" t="n"/>
+    </row>
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="16" t="n"/>
+      <c r="B115" s="16" t="n"/>
+    </row>
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="16" t="n"/>
+      <c r="B116" s="16" t="n"/>
+    </row>
+    <row r="117" ht="14" customHeight="1">
+      <c r="A117" s="16" t="n"/>
+      <c r="B117" s="16" t="n"/>
+    </row>
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="16" t="n"/>
+      <c r="B118" s="16" t="n"/>
+    </row>
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="16" t="n"/>
+      <c r="B119" s="16" t="n"/>
+    </row>
+    <row r="120" ht="14" customHeight="1">
+      <c r="A120" s="16" t="n"/>
+      <c r="B120" s="16" t="n"/>
+    </row>
+    <row r="121" ht="14" customHeight="1">
+      <c r="A121" s="16" t="n"/>
+      <c r="B121" s="16" t="n"/>
+    </row>
+    <row r="122" ht="14" customHeight="1">
+      <c r="A122" s="16" t="n"/>
+      <c r="B122" s="16" t="n"/>
+    </row>
+    <row r="123" ht="14" customHeight="1">
+      <c r="A123" s="16" t="n"/>
+      <c r="B123" s="16" t="n"/>
+    </row>
+    <row r="124" ht="14" customHeight="1">
+      <c r="A124" s="16" t="n"/>
+      <c r="B124" s="16" t="n"/>
+    </row>
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="16" t="n"/>
+      <c r="B125" s="16" t="n"/>
+    </row>
+    <row r="126" ht="10" customHeight="1"/>
+    <row r="127" ht="10" customHeight="1"/>
+    <row r="128" ht="30" customHeight="1">
+      <c r="A128" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-005</t>
+        </is>
+      </c>
+      <c r="B128" s="15" t="inlineStr">
+        <is>
+          <t>staff1 ログイン時 ヘッダーに「ユーザー管理」リンク非表示確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="14" customHeight="1">
+      <c r="A129" s="16" t="n"/>
+      <c r="B129" s="16" t="n"/>
+    </row>
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="16" t="n"/>
+      <c r="B130" s="16" t="n"/>
+    </row>
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="16" t="n"/>
+      <c r="B131" s="16" t="n"/>
+    </row>
+    <row r="132" ht="14" customHeight="1">
+      <c r="A132" s="16" t="n"/>
+      <c r="B132" s="16" t="n"/>
+    </row>
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="16" t="n"/>
+      <c r="B133" s="16" t="n"/>
+    </row>
+    <row r="134" ht="14" customHeight="1">
+      <c r="A134" s="16" t="n"/>
+      <c r="B134" s="16" t="n"/>
+    </row>
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="16" t="n"/>
+      <c r="B135" s="16" t="n"/>
+    </row>
+    <row r="136" ht="14" customHeight="1">
+      <c r="A136" s="16" t="n"/>
+      <c r="B136" s="16" t="n"/>
+    </row>
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="16" t="n"/>
+      <c r="B137" s="16" t="n"/>
+    </row>
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="16" t="n"/>
+      <c r="B138" s="16" t="n"/>
+    </row>
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="16" t="n"/>
+      <c r="B139" s="16" t="n"/>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="16" t="n"/>
+      <c r="B140" s="16" t="n"/>
+    </row>
+    <row r="141" ht="14" customHeight="1">
+      <c r="A141" s="16" t="n"/>
+      <c r="B141" s="16" t="n"/>
+    </row>
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="16" t="n"/>
+      <c r="B142" s="16" t="n"/>
+    </row>
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="16" t="n"/>
+      <c r="B143" s="16" t="n"/>
+    </row>
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="16" t="n"/>
+      <c r="B144" s="16" t="n"/>
+    </row>
+    <row r="145" ht="14" customHeight="1">
+      <c r="A145" s="16" t="n"/>
+      <c r="B145" s="16" t="n"/>
+    </row>
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="16" t="n"/>
+      <c r="B146" s="16" t="n"/>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="16" t="n"/>
+      <c r="B147" s="16" t="n"/>
+    </row>
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="16" t="n"/>
+      <c r="B148" s="16" t="n"/>
+    </row>
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="16" t="n"/>
+      <c r="B149" s="16" t="n"/>
+    </row>
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="16" t="n"/>
+      <c r="B150" s="16" t="n"/>
+    </row>
+    <row r="151" ht="14" customHeight="1">
+      <c r="A151" s="16" t="n"/>
+      <c r="B151" s="16" t="n"/>
+    </row>
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="16" t="n"/>
+      <c r="B152" s="16" t="n"/>
+    </row>
+    <row r="153" ht="14" customHeight="1">
+      <c r="A153" s="16" t="n"/>
+      <c r="B153" s="16" t="n"/>
+    </row>
+    <row r="154" ht="14" customHeight="1">
+      <c r="A154" s="16" t="n"/>
+      <c r="B154" s="16" t="n"/>
+    </row>
+    <row r="155" ht="14" customHeight="1">
+      <c r="A155" s="16" t="n"/>
+      <c r="B155" s="16" t="n"/>
+    </row>
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="16" t="n"/>
+      <c r="B156" s="16" t="n"/>
+    </row>
+    <row r="157" ht="10" customHeight="1"/>
+    <row r="158" ht="10" customHeight="1"/>
+    <row r="159" ht="30" customHeight="1">
+      <c r="A159" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-006</t>
+        </is>
+      </c>
+      <c r="B159" s="15" t="inlineStr">
+        <is>
+          <t>「ログアウト」クリック → login.html 復帰確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="16" t="n"/>
+      <c r="B160" s="16" t="n"/>
+    </row>
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="16" t="n"/>
+      <c r="B161" s="16" t="n"/>
+    </row>
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="16" t="n"/>
+      <c r="B162" s="16" t="n"/>
+    </row>
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="16" t="n"/>
+      <c r="B163" s="16" t="n"/>
+    </row>
+    <row r="164" ht="14" customHeight="1">
+      <c r="A164" s="16" t="n"/>
+      <c r="B164" s="16" t="n"/>
+    </row>
+    <row r="165" ht="14" customHeight="1">
+      <c r="A165" s="16" t="n"/>
+      <c r="B165" s="16" t="n"/>
+    </row>
+    <row r="166" ht="14" customHeight="1">
+      <c r="A166" s="16" t="n"/>
+      <c r="B166" s="16" t="n"/>
+    </row>
+    <row r="167" ht="14" customHeight="1">
+      <c r="A167" s="16" t="n"/>
+      <c r="B167" s="16" t="n"/>
+    </row>
+    <row r="168" ht="14" customHeight="1">
+      <c r="A168" s="16" t="n"/>
+      <c r="B168" s="16" t="n"/>
+    </row>
+    <row r="169" ht="14" customHeight="1">
+      <c r="A169" s="16" t="n"/>
+      <c r="B169" s="16" t="n"/>
+    </row>
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="16" t="n"/>
+      <c r="B170" s="16" t="n"/>
+    </row>
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="16" t="n"/>
+      <c r="B171" s="16" t="n"/>
+    </row>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="16" t="n"/>
+      <c r="B172" s="16" t="n"/>
+    </row>
+    <row r="173" ht="14" customHeight="1">
+      <c r="A173" s="16" t="n"/>
+      <c r="B173" s="16" t="n"/>
+    </row>
+    <row r="174" ht="14" customHeight="1">
+      <c r="A174" s="16" t="n"/>
+      <c r="B174" s="16" t="n"/>
+    </row>
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="16" t="n"/>
+      <c r="B175" s="16" t="n"/>
+    </row>
+    <row r="176" ht="14" customHeight="1">
+      <c r="A176" s="16" t="n"/>
+      <c r="B176" s="16" t="n"/>
+    </row>
+    <row r="177" ht="14" customHeight="1">
+      <c r="A177" s="16" t="n"/>
+      <c r="B177" s="16" t="n"/>
+    </row>
+    <row r="178" ht="14" customHeight="1">
+      <c r="A178" s="16" t="n"/>
+      <c r="B178" s="16" t="n"/>
+    </row>
+    <row r="179" ht="14" customHeight="1">
+      <c r="A179" s="16" t="n"/>
+      <c r="B179" s="16" t="n"/>
+    </row>
+    <row r="180" ht="14" customHeight="1">
+      <c r="A180" s="16" t="n"/>
+      <c r="B180" s="16" t="n"/>
+    </row>
+    <row r="181" ht="14" customHeight="1">
+      <c r="A181" s="16" t="n"/>
+      <c r="B181" s="16" t="n"/>
+    </row>
+    <row r="182" ht="14" customHeight="1">
+      <c r="A182" s="16" t="n"/>
+      <c r="B182" s="16" t="n"/>
+    </row>
+    <row r="183" ht="14" customHeight="1">
+      <c r="A183" s="16" t="n"/>
+      <c r="B183" s="16" t="n"/>
+    </row>
+    <row r="184" ht="14" customHeight="1">
+      <c r="A184" s="16" t="n"/>
+      <c r="B184" s="16" t="n"/>
+    </row>
+    <row r="185" ht="14" customHeight="1">
+      <c r="A185" s="16" t="n"/>
+      <c r="B185" s="16" t="n"/>
+    </row>
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="16" t="n"/>
+      <c r="B186" s="16" t="n"/>
+    </row>
+    <row r="187" ht="14" customHeight="1">
+      <c r="A187" s="16" t="n"/>
+      <c r="B187" s="16" t="n"/>
+    </row>
+    <row r="188" ht="10" customHeight="1"/>
+    <row r="189" ht="10" customHeight="1"/>
+    <row r="190" ht="30" customHeight="1">
+      <c r="A190" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-007</t>
+        </is>
+      </c>
+      <c r="B190" s="15" t="inlineStr">
+        <is>
+          <t>admin ログイン → ダッシュボード遷移・ロール「管理者」表示確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="14" customHeight="1">
+      <c r="A191" s="16" t="n"/>
+      <c r="B191" s="16" t="n"/>
+    </row>
+    <row r="192" ht="14" customHeight="1">
+      <c r="A192" s="16" t="n"/>
+      <c r="B192" s="16" t="n"/>
+    </row>
+    <row r="193" ht="14" customHeight="1">
+      <c r="A193" s="16" t="n"/>
+      <c r="B193" s="16" t="n"/>
+    </row>
+    <row r="194" ht="14" customHeight="1">
+      <c r="A194" s="16" t="n"/>
+      <c r="B194" s="16" t="n"/>
+    </row>
+    <row r="195" ht="14" customHeight="1">
+      <c r="A195" s="16" t="n"/>
+      <c r="B195" s="16" t="n"/>
+    </row>
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="16" t="n"/>
+      <c r="B196" s="16" t="n"/>
+    </row>
+    <row r="197" ht="14" customHeight="1">
+      <c r="A197" s="16" t="n"/>
+      <c r="B197" s="16" t="n"/>
+    </row>
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="16" t="n"/>
+      <c r="B198" s="16" t="n"/>
+    </row>
+    <row r="199" ht="14" customHeight="1">
+      <c r="A199" s="16" t="n"/>
+      <c r="B199" s="16" t="n"/>
+    </row>
+    <row r="200" ht="14" customHeight="1">
+      <c r="A200" s="16" t="n"/>
+      <c r="B200" s="16" t="n"/>
+    </row>
+    <row r="201" ht="14" customHeight="1">
+      <c r="A201" s="16" t="n"/>
+      <c r="B201" s="16" t="n"/>
+    </row>
+    <row r="202" ht="14" customHeight="1">
+      <c r="A202" s="16" t="n"/>
+      <c r="B202" s="16" t="n"/>
+    </row>
+    <row r="203" ht="14" customHeight="1">
+      <c r="A203" s="16" t="n"/>
+      <c r="B203" s="16" t="n"/>
+    </row>
+    <row r="204" ht="14" customHeight="1">
+      <c r="A204" s="16" t="n"/>
+      <c r="B204" s="16" t="n"/>
+    </row>
+    <row r="205" ht="14" customHeight="1">
+      <c r="A205" s="16" t="n"/>
+      <c r="B205" s="16" t="n"/>
+    </row>
+    <row r="206" ht="14" customHeight="1">
+      <c r="A206" s="16" t="n"/>
+      <c r="B206" s="16" t="n"/>
+    </row>
+    <row r="207" ht="14" customHeight="1">
+      <c r="A207" s="16" t="n"/>
+      <c r="B207" s="16" t="n"/>
+    </row>
+    <row r="208" ht="14" customHeight="1">
+      <c r="A208" s="16" t="n"/>
+      <c r="B208" s="16" t="n"/>
+    </row>
+    <row r="209" ht="14" customHeight="1">
+      <c r="A209" s="16" t="n"/>
+      <c r="B209" s="16" t="n"/>
+    </row>
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="16" t="n"/>
+      <c r="B210" s="16" t="n"/>
+    </row>
+    <row r="211" ht="14" customHeight="1">
+      <c r="A211" s="16" t="n"/>
+      <c r="B211" s="16" t="n"/>
+    </row>
+    <row r="212" ht="14" customHeight="1">
+      <c r="A212" s="16" t="n"/>
+      <c r="B212" s="16" t="n"/>
+    </row>
+    <row r="213" ht="14" customHeight="1">
+      <c r="A213" s="16" t="n"/>
+      <c r="B213" s="16" t="n"/>
+    </row>
+    <row r="214" ht="14" customHeight="1">
+      <c r="A214" s="16" t="n"/>
+      <c r="B214" s="16" t="n"/>
+    </row>
+    <row r="215" ht="14" customHeight="1">
+      <c r="A215" s="16" t="n"/>
+      <c r="B215" s="16" t="n"/>
+    </row>
+    <row r="216" ht="14" customHeight="1">
+      <c r="A216" s="16" t="n"/>
+      <c r="B216" s="16" t="n"/>
+    </row>
+    <row r="217" ht="14" customHeight="1">
+      <c r="A217" s="16" t="n"/>
+      <c r="B217" s="16" t="n"/>
+    </row>
+    <row r="218" ht="14" customHeight="1">
+      <c r="A218" s="16" t="n"/>
+      <c r="B218" s="16" t="n"/>
+    </row>
+    <row r="219" ht="10" customHeight="1"/>
+    <row r="220" ht="10" customHeight="1"/>
+    <row r="221" ht="30" customHeight="1">
+      <c r="A221" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-008</t>
+        </is>
+      </c>
+      <c r="B221" s="15" t="inlineStr">
+        <is>
+          <t>全メニューボタン活性状態確認（admin・保険金支払状況も活性）</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="14" customHeight="1">
+      <c r="A222" s="16" t="n"/>
+      <c r="B222" s="16" t="n"/>
+    </row>
+    <row r="223" ht="14" customHeight="1">
+      <c r="A223" s="16" t="n"/>
+      <c r="B223" s="16" t="n"/>
+    </row>
+    <row r="224" ht="14" customHeight="1">
+      <c r="A224" s="16" t="n"/>
+      <c r="B224" s="16" t="n"/>
+    </row>
+    <row r="225" ht="14" customHeight="1">
+      <c r="A225" s="16" t="n"/>
+      <c r="B225" s="16" t="n"/>
+    </row>
+    <row r="226" ht="14" customHeight="1">
+      <c r="A226" s="16" t="n"/>
+      <c r="B226" s="16" t="n"/>
+    </row>
+    <row r="227" ht="14" customHeight="1">
+      <c r="A227" s="16" t="n"/>
+      <c r="B227" s="16" t="n"/>
+    </row>
+    <row r="228" ht="14" customHeight="1">
+      <c r="A228" s="16" t="n"/>
+      <c r="B228" s="16" t="n"/>
+    </row>
+    <row r="229" ht="14" customHeight="1">
+      <c r="A229" s="16" t="n"/>
+      <c r="B229" s="16" t="n"/>
+    </row>
+    <row r="230" ht="14" customHeight="1">
+      <c r="A230" s="16" t="n"/>
+      <c r="B230" s="16" t="n"/>
+    </row>
+    <row r="231" ht="14" customHeight="1">
+      <c r="A231" s="16" t="n"/>
+      <c r="B231" s="16" t="n"/>
+    </row>
+    <row r="232" ht="14" customHeight="1">
+      <c r="A232" s="16" t="n"/>
+      <c r="B232" s="16" t="n"/>
+    </row>
+    <row r="233" ht="14" customHeight="1">
+      <c r="A233" s="16" t="n"/>
+      <c r="B233" s="16" t="n"/>
+    </row>
+    <row r="234" ht="14" customHeight="1">
+      <c r="A234" s="16" t="n"/>
+      <c r="B234" s="16" t="n"/>
+    </row>
+    <row r="235" ht="14" customHeight="1">
+      <c r="A235" s="16" t="n"/>
+      <c r="B235" s="16" t="n"/>
+    </row>
+    <row r="236" ht="14" customHeight="1">
+      <c r="A236" s="16" t="n"/>
+      <c r="B236" s="16" t="n"/>
+    </row>
+    <row r="237" ht="14" customHeight="1">
+      <c r="A237" s="16" t="n"/>
+      <c r="B237" s="16" t="n"/>
+    </row>
+    <row r="238" ht="14" customHeight="1">
+      <c r="A238" s="16" t="n"/>
+      <c r="B238" s="16" t="n"/>
+    </row>
+    <row r="239" ht="14" customHeight="1">
+      <c r="A239" s="16" t="n"/>
+      <c r="B239" s="16" t="n"/>
+    </row>
+    <row r="240" ht="14" customHeight="1">
+      <c r="A240" s="16" t="n"/>
+      <c r="B240" s="16" t="n"/>
+    </row>
+    <row r="241" ht="14" customHeight="1">
+      <c r="A241" s="16" t="n"/>
+      <c r="B241" s="16" t="n"/>
+    </row>
+    <row r="242" ht="14" customHeight="1">
+      <c r="A242" s="16" t="n"/>
+      <c r="B242" s="16" t="n"/>
+    </row>
+    <row r="243" ht="14" customHeight="1">
+      <c r="A243" s="16" t="n"/>
+      <c r="B243" s="16" t="n"/>
+    </row>
+    <row r="244" ht="14" customHeight="1">
+      <c r="A244" s="16" t="n"/>
+      <c r="B244" s="16" t="n"/>
+    </row>
+    <row r="245" ht="14" customHeight="1">
+      <c r="A245" s="16" t="n"/>
+      <c r="B245" s="16" t="n"/>
+    </row>
+    <row r="246" ht="14" customHeight="1">
+      <c r="A246" s="16" t="n"/>
+      <c r="B246" s="16" t="n"/>
+    </row>
+    <row r="247" ht="14" customHeight="1">
+      <c r="A247" s="16" t="n"/>
+      <c r="B247" s="16" t="n"/>
+    </row>
+    <row r="248" ht="14" customHeight="1">
+      <c r="A248" s="16" t="n"/>
+      <c r="B248" s="16" t="n"/>
+    </row>
+    <row r="249" ht="14" customHeight="1">
+      <c r="A249" s="16" t="n"/>
+      <c r="B249" s="16" t="n"/>
+    </row>
+    <row r="250" ht="10" customHeight="1"/>
+    <row r="251" ht="10" customHeight="1"/>
+    <row r="252" ht="30" customHeight="1">
+      <c r="A252" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-009</t>
+        </is>
+      </c>
+      <c r="B252" s="15" t="inlineStr">
+        <is>
+          <t>ヘッダーに「ユーザー管理」リンク表示確認（admin）</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="14" customHeight="1">
+      <c r="A253" s="16" t="n"/>
+      <c r="B253" s="16" t="n"/>
+    </row>
+    <row r="254" ht="14" customHeight="1">
+      <c r="A254" s="16" t="n"/>
+      <c r="B254" s="16" t="n"/>
+    </row>
+    <row r="255" ht="14" customHeight="1">
+      <c r="A255" s="16" t="n"/>
+      <c r="B255" s="16" t="n"/>
+    </row>
+    <row r="256" ht="14" customHeight="1">
+      <c r="A256" s="16" t="n"/>
+      <c r="B256" s="16" t="n"/>
+    </row>
+    <row r="257" ht="14" customHeight="1">
+      <c r="A257" s="16" t="n"/>
+      <c r="B257" s="16" t="n"/>
+    </row>
+    <row r="258" ht="14" customHeight="1">
+      <c r="A258" s="16" t="n"/>
+      <c r="B258" s="16" t="n"/>
+    </row>
+    <row r="259" ht="14" customHeight="1">
+      <c r="A259" s="16" t="n"/>
+      <c r="B259" s="16" t="n"/>
+    </row>
+    <row r="260" ht="14" customHeight="1">
+      <c r="A260" s="16" t="n"/>
+      <c r="B260" s="16" t="n"/>
+    </row>
+    <row r="261" ht="14" customHeight="1">
+      <c r="A261" s="16" t="n"/>
+      <c r="B261" s="16" t="n"/>
+    </row>
+    <row r="262" ht="14" customHeight="1">
+      <c r="A262" s="16" t="n"/>
+      <c r="B262" s="16" t="n"/>
+    </row>
+    <row r="263" ht="14" customHeight="1">
+      <c r="A263" s="16" t="n"/>
+      <c r="B263" s="16" t="n"/>
+    </row>
+    <row r="264" ht="14" customHeight="1">
+      <c r="A264" s="16" t="n"/>
+      <c r="B264" s="16" t="n"/>
+    </row>
+    <row r="265" ht="14" customHeight="1">
+      <c r="A265" s="16" t="n"/>
+      <c r="B265" s="16" t="n"/>
+    </row>
+    <row r="266" ht="14" customHeight="1">
+      <c r="A266" s="16" t="n"/>
+      <c r="B266" s="16" t="n"/>
+    </row>
+    <row r="267" ht="14" customHeight="1">
+      <c r="A267" s="16" t="n"/>
+      <c r="B267" s="16" t="n"/>
+    </row>
+    <row r="268" ht="14" customHeight="1">
+      <c r="A268" s="16" t="n"/>
+      <c r="B268" s="16" t="n"/>
+    </row>
+    <row r="269" ht="14" customHeight="1">
+      <c r="A269" s="16" t="n"/>
+      <c r="B269" s="16" t="n"/>
+    </row>
+    <row r="270" ht="14" customHeight="1">
+      <c r="A270" s="16" t="n"/>
+      <c r="B270" s="16" t="n"/>
+    </row>
+    <row r="271" ht="14" customHeight="1">
+      <c r="A271" s="16" t="n"/>
+      <c r="B271" s="16" t="n"/>
+    </row>
+    <row r="272" ht="14" customHeight="1">
+      <c r="A272" s="16" t="n"/>
+      <c r="B272" s="16" t="n"/>
+    </row>
+    <row r="273" ht="14" customHeight="1">
+      <c r="A273" s="16" t="n"/>
+      <c r="B273" s="16" t="n"/>
+    </row>
+    <row r="274" ht="14" customHeight="1">
+      <c r="A274" s="16" t="n"/>
+      <c r="B274" s="16" t="n"/>
+    </row>
+    <row r="275" ht="14" customHeight="1">
+      <c r="A275" s="16" t="n"/>
+      <c r="B275" s="16" t="n"/>
+    </row>
+    <row r="276" ht="14" customHeight="1">
+      <c r="A276" s="16" t="n"/>
+      <c r="B276" s="16" t="n"/>
+    </row>
+    <row r="277" ht="14" customHeight="1">
+      <c r="A277" s="16" t="n"/>
+      <c r="B277" s="16" t="n"/>
+    </row>
+    <row r="278" ht="14" customHeight="1">
+      <c r="A278" s="16" t="n"/>
+      <c r="B278" s="16" t="n"/>
+    </row>
+    <row r="279" ht="14" customHeight="1">
+      <c r="A279" s="16" t="n"/>
+      <c r="B279" s="16" t="n"/>
+    </row>
+    <row r="280" ht="14" customHeight="1">
+      <c r="A280" s="16" t="n"/>
+      <c r="B280" s="16" t="n"/>
+    </row>
+    <row r="281" ht="10" customHeight="1"/>
+    <row r="282" ht="10" customHeight="1"/>
+    <row r="283" ht="30" customHeight="1">
+      <c r="A283" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-010</t>
+        </is>
+      </c>
+      <c r="B283" s="15" t="inlineStr">
+        <is>
+          <t>「ユーザー管理」リンク → admin.html 遷移確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="14" customHeight="1">
+      <c r="A284" s="16" t="n"/>
+      <c r="B284" s="16" t="n"/>
+    </row>
+    <row r="285" ht="14" customHeight="1">
+      <c r="A285" s="16" t="n"/>
+      <c r="B285" s="16" t="n"/>
+    </row>
+    <row r="286" ht="14" customHeight="1">
+      <c r="A286" s="16" t="n"/>
+      <c r="B286" s="16" t="n"/>
+    </row>
+    <row r="287" ht="14" customHeight="1">
+      <c r="A287" s="16" t="n"/>
+      <c r="B287" s="16" t="n"/>
+    </row>
+    <row r="288" ht="14" customHeight="1">
+      <c r="A288" s="16" t="n"/>
+      <c r="B288" s="16" t="n"/>
+    </row>
+    <row r="289" ht="14" customHeight="1">
+      <c r="A289" s="16" t="n"/>
+      <c r="B289" s="16" t="n"/>
+    </row>
+    <row r="290" ht="14" customHeight="1">
+      <c r="A290" s="16" t="n"/>
+      <c r="B290" s="16" t="n"/>
+    </row>
+    <row r="291" ht="14" customHeight="1">
+      <c r="A291" s="16" t="n"/>
+      <c r="B291" s="16" t="n"/>
+    </row>
+    <row r="292" ht="14" customHeight="1">
+      <c r="A292" s="16" t="n"/>
+      <c r="B292" s="16" t="n"/>
+    </row>
+    <row r="293" ht="14" customHeight="1">
+      <c r="A293" s="16" t="n"/>
+      <c r="B293" s="16" t="n"/>
+    </row>
+    <row r="294" ht="14" customHeight="1">
+      <c r="A294" s="16" t="n"/>
+      <c r="B294" s="16" t="n"/>
+    </row>
+    <row r="295" ht="14" customHeight="1">
+      <c r="A295" s="16" t="n"/>
+      <c r="B295" s="16" t="n"/>
+    </row>
+    <row r="296" ht="14" customHeight="1">
+      <c r="A296" s="16" t="n"/>
+      <c r="B296" s="16" t="n"/>
+    </row>
+    <row r="297" ht="14" customHeight="1">
+      <c r="A297" s="16" t="n"/>
+      <c r="B297" s="16" t="n"/>
+    </row>
+    <row r="298" ht="14" customHeight="1">
+      <c r="A298" s="16" t="n"/>
+      <c r="B298" s="16" t="n"/>
+    </row>
+    <row r="299" ht="14" customHeight="1">
+      <c r="A299" s="16" t="n"/>
+      <c r="B299" s="16" t="n"/>
+    </row>
+    <row r="300" ht="14" customHeight="1">
+      <c r="A300" s="16" t="n"/>
+      <c r="B300" s="16" t="n"/>
+    </row>
+    <row r="301" ht="14" customHeight="1">
+      <c r="A301" s="16" t="n"/>
+      <c r="B301" s="16" t="n"/>
+    </row>
+    <row r="302" ht="14" customHeight="1">
+      <c r="A302" s="16" t="n"/>
+      <c r="B302" s="16" t="n"/>
+    </row>
+    <row r="303" ht="14" customHeight="1">
+      <c r="A303" s="16" t="n"/>
+      <c r="B303" s="16" t="n"/>
+    </row>
+    <row r="304" ht="14" customHeight="1">
+      <c r="A304" s="16" t="n"/>
+      <c r="B304" s="16" t="n"/>
+    </row>
+    <row r="305" ht="14" customHeight="1">
+      <c r="A305" s="16" t="n"/>
+      <c r="B305" s="16" t="n"/>
+    </row>
+    <row r="306" ht="14" customHeight="1">
+      <c r="A306" s="16" t="n"/>
+      <c r="B306" s="16" t="n"/>
+    </row>
+    <row r="307" ht="14" customHeight="1">
+      <c r="A307" s="16" t="n"/>
+      <c r="B307" s="16" t="n"/>
+    </row>
+    <row r="308" ht="14" customHeight="1">
+      <c r="A308" s="16" t="n"/>
+      <c r="B308" s="16" t="n"/>
+    </row>
+    <row r="309" ht="14" customHeight="1">
+      <c r="A309" s="16" t="n"/>
+      <c r="B309" s="16" t="n"/>
+    </row>
+    <row r="310" ht="14" customHeight="1">
+      <c r="A310" s="16" t="n"/>
+      <c r="B310" s="16" t="n"/>
+    </row>
+    <row r="311" ht="14" customHeight="1">
+      <c r="A311" s="16" t="n"/>
+      <c r="B311" s="16" t="n"/>
+    </row>
+    <row r="312" ht="10" customHeight="1"/>
+    <row r="313" ht="10" customHeight="1"/>
+    <row r="314" ht="30" customHeight="1">
+      <c r="A314" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-011</t>
+        </is>
+      </c>
+      <c r="B314" s="15" t="inlineStr">
+        <is>
+          <t>ユーザー一覧テーブル（admin・staff1の2件）・ロールチップ・操作ボタン確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="14" customHeight="1">
+      <c r="A315" s="16" t="n"/>
+      <c r="B315" s="16" t="n"/>
+    </row>
+    <row r="316" ht="14" customHeight="1">
+      <c r="A316" s="16" t="n"/>
+      <c r="B316" s="16" t="n"/>
+    </row>
+    <row r="317" ht="14" customHeight="1">
+      <c r="A317" s="16" t="n"/>
+      <c r="B317" s="16" t="n"/>
+    </row>
+    <row r="318" ht="14" customHeight="1">
+      <c r="A318" s="16" t="n"/>
+      <c r="B318" s="16" t="n"/>
+    </row>
+    <row r="319" ht="14" customHeight="1">
+      <c r="A319" s="16" t="n"/>
+      <c r="B319" s="16" t="n"/>
+    </row>
+    <row r="320" ht="14" customHeight="1">
+      <c r="A320" s="16" t="n"/>
+      <c r="B320" s="16" t="n"/>
+    </row>
+    <row r="321" ht="14" customHeight="1">
+      <c r="A321" s="16" t="n"/>
+      <c r="B321" s="16" t="n"/>
+    </row>
+    <row r="322" ht="14" customHeight="1">
+      <c r="A322" s="16" t="n"/>
+      <c r="B322" s="16" t="n"/>
+    </row>
+    <row r="323" ht="14" customHeight="1">
+      <c r="A323" s="16" t="n"/>
+      <c r="B323" s="16" t="n"/>
+    </row>
+    <row r="324" ht="14" customHeight="1">
+      <c r="A324" s="16" t="n"/>
+      <c r="B324" s="16" t="n"/>
+    </row>
+    <row r="325" ht="14" customHeight="1">
+      <c r="A325" s="16" t="n"/>
+      <c r="B325" s="16" t="n"/>
+    </row>
+    <row r="326" ht="14" customHeight="1">
+      <c r="A326" s="16" t="n"/>
+      <c r="B326" s="16" t="n"/>
+    </row>
+    <row r="327" ht="14" customHeight="1">
+      <c r="A327" s="16" t="n"/>
+      <c r="B327" s="16" t="n"/>
+    </row>
+    <row r="328" ht="14" customHeight="1">
+      <c r="A328" s="16" t="n"/>
+      <c r="B328" s="16" t="n"/>
+    </row>
+    <row r="329" ht="14" customHeight="1">
+      <c r="A329" s="16" t="n"/>
+      <c r="B329" s="16" t="n"/>
+    </row>
+    <row r="330" ht="14" customHeight="1">
+      <c r="A330" s="16" t="n"/>
+      <c r="B330" s="16" t="n"/>
+    </row>
+    <row r="331" ht="14" customHeight="1">
+      <c r="A331" s="16" t="n"/>
+      <c r="B331" s="16" t="n"/>
+    </row>
+    <row r="332" ht="14" customHeight="1">
+      <c r="A332" s="16" t="n"/>
+      <c r="B332" s="16" t="n"/>
+    </row>
+    <row r="333" ht="14" customHeight="1">
+      <c r="A333" s="16" t="n"/>
+      <c r="B333" s="16" t="n"/>
+    </row>
+    <row r="334" ht="14" customHeight="1">
+      <c r="A334" s="16" t="n"/>
+      <c r="B334" s="16" t="n"/>
+    </row>
+    <row r="335" ht="14" customHeight="1">
+      <c r="A335" s="16" t="n"/>
+      <c r="B335" s="16" t="n"/>
+    </row>
+    <row r="336" ht="14" customHeight="1">
+      <c r="A336" s="16" t="n"/>
+      <c r="B336" s="16" t="n"/>
+    </row>
+    <row r="337" ht="14" customHeight="1">
+      <c r="A337" s="16" t="n"/>
+      <c r="B337" s="16" t="n"/>
+    </row>
+    <row r="338" ht="14" customHeight="1">
+      <c r="A338" s="16" t="n"/>
+      <c r="B338" s="16" t="n"/>
+    </row>
+    <row r="339" ht="14" customHeight="1">
+      <c r="A339" s="16" t="n"/>
+      <c r="B339" s="16" t="n"/>
+    </row>
+    <row r="340" ht="14" customHeight="1">
+      <c r="A340" s="16" t="n"/>
+      <c r="B340" s="16" t="n"/>
+    </row>
+    <row r="341" ht="14" customHeight="1">
+      <c r="A341" s="16" t="n"/>
+      <c r="B341" s="16" t="n"/>
+    </row>
+    <row r="342" ht="14" customHeight="1">
+      <c r="A342" s="16" t="n"/>
+      <c r="B342" s="16" t="n"/>
+    </row>
+    <row r="343" ht="10" customHeight="1"/>
+    <row r="344" ht="10" customHeight="1"/>
+    <row r="345" ht="30" customHeight="1">
+      <c r="A345" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-012</t>
+        </is>
+      </c>
+      <c r="B345" s="15" t="inlineStr">
+        <is>
+          <t>「＋ユーザー追加」ボタン → 追加モーダル表示確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="14" customHeight="1">
+      <c r="A346" s="16" t="n"/>
+      <c r="B346" s="16" t="n"/>
+    </row>
+    <row r="347" ht="14" customHeight="1">
+      <c r="A347" s="16" t="n"/>
+      <c r="B347" s="16" t="n"/>
+    </row>
+    <row r="348" ht="14" customHeight="1">
+      <c r="A348" s="16" t="n"/>
+      <c r="B348" s="16" t="n"/>
+    </row>
+    <row r="349" ht="14" customHeight="1">
+      <c r="A349" s="16" t="n"/>
+      <c r="B349" s="16" t="n"/>
+    </row>
+    <row r="350" ht="14" customHeight="1">
+      <c r="A350" s="16" t="n"/>
+      <c r="B350" s="16" t="n"/>
+    </row>
+    <row r="351" ht="14" customHeight="1">
+      <c r="A351" s="16" t="n"/>
+      <c r="B351" s="16" t="n"/>
+    </row>
+    <row r="352" ht="14" customHeight="1">
+      <c r="A352" s="16" t="n"/>
+      <c r="B352" s="16" t="n"/>
+    </row>
+    <row r="353" ht="14" customHeight="1">
+      <c r="A353" s="16" t="n"/>
+      <c r="B353" s="16" t="n"/>
+    </row>
+    <row r="354" ht="14" customHeight="1">
+      <c r="A354" s="16" t="n"/>
+      <c r="B354" s="16" t="n"/>
+    </row>
+    <row r="355" ht="14" customHeight="1">
+      <c r="A355" s="16" t="n"/>
+      <c r="B355" s="16" t="n"/>
+    </row>
+    <row r="356" ht="14" customHeight="1">
+      <c r="A356" s="16" t="n"/>
+      <c r="B356" s="16" t="n"/>
+    </row>
+    <row r="357" ht="14" customHeight="1">
+      <c r="A357" s="16" t="n"/>
+      <c r="B357" s="16" t="n"/>
+    </row>
+    <row r="358" ht="14" customHeight="1">
+      <c r="A358" s="16" t="n"/>
+      <c r="B358" s="16" t="n"/>
+    </row>
+    <row r="359" ht="14" customHeight="1">
+      <c r="A359" s="16" t="n"/>
+      <c r="B359" s="16" t="n"/>
+    </row>
+    <row r="360" ht="14" customHeight="1">
+      <c r="A360" s="16" t="n"/>
+      <c r="B360" s="16" t="n"/>
+    </row>
+    <row r="361" ht="14" customHeight="1">
+      <c r="A361" s="16" t="n"/>
+      <c r="B361" s="16" t="n"/>
+    </row>
+    <row r="362" ht="14" customHeight="1">
+      <c r="A362" s="16" t="n"/>
+      <c r="B362" s="16" t="n"/>
+    </row>
+    <row r="363" ht="14" customHeight="1">
+      <c r="A363" s="16" t="n"/>
+      <c r="B363" s="16" t="n"/>
+    </row>
+    <row r="364" ht="14" customHeight="1">
+      <c r="A364" s="16" t="n"/>
+      <c r="B364" s="16" t="n"/>
+    </row>
+    <row r="365" ht="14" customHeight="1">
+      <c r="A365" s="16" t="n"/>
+      <c r="B365" s="16" t="n"/>
+    </row>
+    <row r="366" ht="14" customHeight="1">
+      <c r="A366" s="16" t="n"/>
+      <c r="B366" s="16" t="n"/>
+    </row>
+    <row r="367" ht="14" customHeight="1">
+      <c r="A367" s="16" t="n"/>
+      <c r="B367" s="16" t="n"/>
+    </row>
+    <row r="368" ht="14" customHeight="1">
+      <c r="A368" s="16" t="n"/>
+      <c r="B368" s="16" t="n"/>
+    </row>
+    <row r="369" ht="14" customHeight="1">
+      <c r="A369" s="16" t="n"/>
+      <c r="B369" s="16" t="n"/>
+    </row>
+    <row r="370" ht="14" customHeight="1">
+      <c r="A370" s="16" t="n"/>
+      <c r="B370" s="16" t="n"/>
+    </row>
+    <row r="371" ht="14" customHeight="1">
+      <c r="A371" s="16" t="n"/>
+      <c r="B371" s="16" t="n"/>
+    </row>
+    <row r="372" ht="14" customHeight="1">
+      <c r="A372" s="16" t="n"/>
+      <c r="B372" s="16" t="n"/>
+    </row>
+    <row r="373" ht="14" customHeight="1">
+      <c r="A373" s="16" t="n"/>
+      <c r="B373" s="16" t="n"/>
+    </row>
+    <row r="374" ht="10" customHeight="1"/>
+    <row r="375" ht="10" customHeight="1"/>
+    <row r="376" ht="30" customHeight="1">
+      <c r="A376" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-013</t>
+        </is>
+      </c>
+      <c r="B376" s="15" t="inlineStr">
+        <is>
+          <t>ロール別権限マトリクス表示確認（管理者=全権限、一般担当・閲覧専用=制限あり）</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="14" customHeight="1">
+      <c r="A377" s="16" t="n"/>
+      <c r="B377" s="16" t="n"/>
+    </row>
+    <row r="378" ht="14" customHeight="1">
+      <c r="A378" s="16" t="n"/>
+      <c r="B378" s="16" t="n"/>
+    </row>
+    <row r="379" ht="14" customHeight="1">
+      <c r="A379" s="16" t="n"/>
+      <c r="B379" s="16" t="n"/>
+    </row>
+    <row r="380" ht="14" customHeight="1">
+      <c r="A380" s="16" t="n"/>
+      <c r="B380" s="16" t="n"/>
+    </row>
+    <row r="381" ht="14" customHeight="1">
+      <c r="A381" s="16" t="n"/>
+      <c r="B381" s="16" t="n"/>
+    </row>
+    <row r="382" ht="14" customHeight="1">
+      <c r="A382" s="16" t="n"/>
+      <c r="B382" s="16" t="n"/>
+    </row>
+    <row r="383" ht="14" customHeight="1">
+      <c r="A383" s="16" t="n"/>
+      <c r="B383" s="16" t="n"/>
+    </row>
+    <row r="384" ht="14" customHeight="1">
+      <c r="A384" s="16" t="n"/>
+      <c r="B384" s="16" t="n"/>
+    </row>
+    <row r="385" ht="14" customHeight="1">
+      <c r="A385" s="16" t="n"/>
+      <c r="B385" s="16" t="n"/>
+    </row>
+    <row r="386" ht="14" customHeight="1">
+      <c r="A386" s="16" t="n"/>
+      <c r="B386" s="16" t="n"/>
+    </row>
+    <row r="387" ht="14" customHeight="1">
+      <c r="A387" s="16" t="n"/>
+      <c r="B387" s="16" t="n"/>
+    </row>
+    <row r="388" ht="14" customHeight="1">
+      <c r="A388" s="16" t="n"/>
+      <c r="B388" s="16" t="n"/>
+    </row>
+    <row r="389" ht="14" customHeight="1">
+      <c r="A389" s="16" t="n"/>
+      <c r="B389" s="16" t="n"/>
+    </row>
+    <row r="390" ht="14" customHeight="1">
+      <c r="A390" s="16" t="n"/>
+      <c r="B390" s="16" t="n"/>
+    </row>
+    <row r="391" ht="14" customHeight="1">
+      <c r="A391" s="16" t="n"/>
+      <c r="B391" s="16" t="n"/>
+    </row>
+    <row r="392" ht="14" customHeight="1">
+      <c r="A392" s="16" t="n"/>
+      <c r="B392" s="16" t="n"/>
+    </row>
+    <row r="393" ht="14" customHeight="1">
+      <c r="A393" s="16" t="n"/>
+      <c r="B393" s="16" t="n"/>
+    </row>
+    <row r="394" ht="14" customHeight="1">
+      <c r="A394" s="16" t="n"/>
+      <c r="B394" s="16" t="n"/>
+    </row>
+    <row r="395" ht="14" customHeight="1">
+      <c r="A395" s="16" t="n"/>
+      <c r="B395" s="16" t="n"/>
+    </row>
+    <row r="396" ht="14" customHeight="1">
+      <c r="A396" s="16" t="n"/>
+      <c r="B396" s="16" t="n"/>
+    </row>
+    <row r="397" ht="14" customHeight="1">
+      <c r="A397" s="16" t="n"/>
+      <c r="B397" s="16" t="n"/>
+    </row>
+    <row r="398" ht="14" customHeight="1">
+      <c r="A398" s="16" t="n"/>
+      <c r="B398" s="16" t="n"/>
+    </row>
+    <row r="399" ht="14" customHeight="1">
+      <c r="A399" s="16" t="n"/>
+      <c r="B399" s="16" t="n"/>
+    </row>
+    <row r="400" ht="14" customHeight="1">
+      <c r="A400" s="16" t="n"/>
+      <c r="B400" s="16" t="n"/>
+    </row>
+    <row r="401" ht="14" customHeight="1">
+      <c r="A401" s="16" t="n"/>
+      <c r="B401" s="16" t="n"/>
+    </row>
+    <row r="402" ht="14" customHeight="1">
+      <c r="A402" s="16" t="n"/>
+      <c r="B402" s="16" t="n"/>
+    </row>
+    <row r="403" ht="14" customHeight="1">
+      <c r="A403" s="16" t="n"/>
+      <c r="B403" s="16" t="n"/>
+    </row>
+    <row r="404" ht="14" customHeight="1">
+      <c r="A404" s="16" t="n"/>
+      <c r="B404" s="16" t="n"/>
+    </row>
+    <row r="405" ht="10" customHeight="1"/>
+    <row r="406" ht="10" customHeight="1"/>
+    <row r="407" ht="30" customHeight="1">
+      <c r="A407" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-014</t>
+        </is>
+      </c>
+      <c r="B407" s="15" t="inlineStr">
+        <is>
+          <t>GET /api/permissions (staff1) → 一般担当権限制御がダッシュボードに反映されていることで確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="14" customHeight="1">
+      <c r="A408" s="16" t="n"/>
+      <c r="B408" s="16" t="n"/>
+    </row>
+    <row r="409" ht="14" customHeight="1">
+      <c r="A409" s="16" t="n"/>
+      <c r="B409" s="16" t="n"/>
+    </row>
+    <row r="410" ht="14" customHeight="1">
+      <c r="A410" s="16" t="n"/>
+      <c r="B410" s="16" t="n"/>
+    </row>
+    <row r="411" ht="14" customHeight="1">
+      <c r="A411" s="16" t="n"/>
+      <c r="B411" s="16" t="n"/>
+    </row>
+    <row r="412" ht="14" customHeight="1">
+      <c r="A412" s="16" t="n"/>
+      <c r="B412" s="16" t="n"/>
+    </row>
+    <row r="413" ht="14" customHeight="1">
+      <c r="A413" s="16" t="n"/>
+      <c r="B413" s="16" t="n"/>
+    </row>
+    <row r="414" ht="14" customHeight="1">
+      <c r="A414" s="16" t="n"/>
+      <c r="B414" s="16" t="n"/>
+    </row>
+    <row r="415" ht="14" customHeight="1">
+      <c r="A415" s="16" t="n"/>
+      <c r="B415" s="16" t="n"/>
+    </row>
+    <row r="416" ht="14" customHeight="1">
+      <c r="A416" s="16" t="n"/>
+      <c r="B416" s="16" t="n"/>
+    </row>
+    <row r="417" ht="14" customHeight="1">
+      <c r="A417" s="16" t="n"/>
+      <c r="B417" s="16" t="n"/>
+    </row>
+    <row r="418" ht="14" customHeight="1">
+      <c r="A418" s="16" t="n"/>
+      <c r="B418" s="16" t="n"/>
+    </row>
+    <row r="419" ht="14" customHeight="1">
+      <c r="A419" s="16" t="n"/>
+      <c r="B419" s="16" t="n"/>
+    </row>
+    <row r="420" ht="14" customHeight="1">
+      <c r="A420" s="16" t="n"/>
+      <c r="B420" s="16" t="n"/>
+    </row>
+    <row r="421" ht="14" customHeight="1">
+      <c r="A421" s="16" t="n"/>
+      <c r="B421" s="16" t="n"/>
+    </row>
+    <row r="422" ht="14" customHeight="1">
+      <c r="A422" s="16" t="n"/>
+      <c r="B422" s="16" t="n"/>
+    </row>
+    <row r="423" ht="14" customHeight="1">
+      <c r="A423" s="16" t="n"/>
+      <c r="B423" s="16" t="n"/>
+    </row>
+    <row r="424" ht="14" customHeight="1">
+      <c r="A424" s="16" t="n"/>
+      <c r="B424" s="16" t="n"/>
+    </row>
+    <row r="425" ht="14" customHeight="1">
+      <c r="A425" s="16" t="n"/>
+      <c r="B425" s="16" t="n"/>
+    </row>
+    <row r="426" ht="14" customHeight="1">
+      <c r="A426" s="16" t="n"/>
+      <c r="B426" s="16" t="n"/>
+    </row>
+    <row r="427" ht="14" customHeight="1">
+      <c r="A427" s="16" t="n"/>
+      <c r="B427" s="16" t="n"/>
+    </row>
+    <row r="428" ht="14" customHeight="1">
+      <c r="A428" s="16" t="n"/>
+      <c r="B428" s="16" t="n"/>
+    </row>
+    <row r="429" ht="14" customHeight="1">
+      <c r="A429" s="16" t="n"/>
+      <c r="B429" s="16" t="n"/>
+    </row>
+    <row r="430" ht="14" customHeight="1">
+      <c r="A430" s="16" t="n"/>
+      <c r="B430" s="16" t="n"/>
+    </row>
+    <row r="431" ht="14" customHeight="1">
+      <c r="A431" s="16" t="n"/>
+      <c r="B431" s="16" t="n"/>
+    </row>
+    <row r="432" ht="14" customHeight="1">
+      <c r="A432" s="16" t="n"/>
+      <c r="B432" s="16" t="n"/>
+    </row>
+    <row r="433" ht="14" customHeight="1">
+      <c r="A433" s="16" t="n"/>
+      <c r="B433" s="16" t="n"/>
+    </row>
+    <row r="434" ht="14" customHeight="1">
+      <c r="A434" s="16" t="n"/>
+      <c r="B434" s="16" t="n"/>
+    </row>
+    <row r="435" ht="14" customHeight="1">
+      <c r="A435" s="16" t="n"/>
+      <c r="B435" s="16" t="n"/>
+    </row>
+    <row r="436" ht="10" customHeight="1"/>
+    <row r="437" ht="10" customHeight="1"/>
+    <row r="438" ht="30" customHeight="1">
+      <c r="A438" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-015</t>
+        </is>
+      </c>
+      <c r="B438" s="15" t="inlineStr">
+        <is>
+          <t>GET /api/users (staff1=role_id:2) → 403応答。ユーザー管理リンク非表示・管理画面アクセス不可で確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="14" customHeight="1">
+      <c r="A439" s="16" t="n"/>
+      <c r="B439" s="16" t="n"/>
+    </row>
+    <row r="440" ht="14" customHeight="1">
+      <c r="A440" s="16" t="n"/>
+      <c r="B440" s="16" t="n"/>
+    </row>
+    <row r="441" ht="14" customHeight="1">
+      <c r="A441" s="16" t="n"/>
+      <c r="B441" s="16" t="n"/>
+    </row>
+    <row r="442" ht="14" customHeight="1">
+      <c r="A442" s="16" t="n"/>
+      <c r="B442" s="16" t="n"/>
+    </row>
+    <row r="443" ht="14" customHeight="1">
+      <c r="A443" s="16" t="n"/>
+      <c r="B443" s="16" t="n"/>
+    </row>
+    <row r="444" ht="14" customHeight="1">
+      <c r="A444" s="16" t="n"/>
+      <c r="B444" s="16" t="n"/>
+    </row>
+    <row r="445" ht="14" customHeight="1">
+      <c r="A445" s="16" t="n"/>
+      <c r="B445" s="16" t="n"/>
+    </row>
+    <row r="446" ht="14" customHeight="1">
+      <c r="A446" s="16" t="n"/>
+      <c r="B446" s="16" t="n"/>
+    </row>
+    <row r="447" ht="14" customHeight="1">
+      <c r="A447" s="16" t="n"/>
+      <c r="B447" s="16" t="n"/>
+    </row>
+    <row r="448" ht="14" customHeight="1">
+      <c r="A448" s="16" t="n"/>
+      <c r="B448" s="16" t="n"/>
+    </row>
+    <row r="449" ht="14" customHeight="1">
+      <c r="A449" s="16" t="n"/>
+      <c r="B449" s="16" t="n"/>
+    </row>
+    <row r="450" ht="14" customHeight="1">
+      <c r="A450" s="16" t="n"/>
+      <c r="B450" s="16" t="n"/>
+    </row>
+    <row r="451" ht="14" customHeight="1">
+      <c r="A451" s="16" t="n"/>
+      <c r="B451" s="16" t="n"/>
+    </row>
+    <row r="452" ht="14" customHeight="1">
+      <c r="A452" s="16" t="n"/>
+      <c r="B452" s="16" t="n"/>
+    </row>
+    <row r="453" ht="14" customHeight="1">
+      <c r="A453" s="16" t="n"/>
+      <c r="B453" s="16" t="n"/>
+    </row>
+    <row r="454" ht="14" customHeight="1">
+      <c r="A454" s="16" t="n"/>
+      <c r="B454" s="16" t="n"/>
+    </row>
+    <row r="455" ht="14" customHeight="1">
+      <c r="A455" s="16" t="n"/>
+      <c r="B455" s="16" t="n"/>
+    </row>
+    <row r="456" ht="14" customHeight="1">
+      <c r="A456" s="16" t="n"/>
+      <c r="B456" s="16" t="n"/>
+    </row>
+    <row r="457" ht="14" customHeight="1">
+      <c r="A457" s="16" t="n"/>
+      <c r="B457" s="16" t="n"/>
+    </row>
+    <row r="458" ht="14" customHeight="1">
+      <c r="A458" s="16" t="n"/>
+      <c r="B458" s="16" t="n"/>
+    </row>
+    <row r="459" ht="14" customHeight="1">
+      <c r="A459" s="16" t="n"/>
+      <c r="B459" s="16" t="n"/>
+    </row>
+    <row r="460" ht="14" customHeight="1">
+      <c r="A460" s="16" t="n"/>
+      <c r="B460" s="16" t="n"/>
+    </row>
+    <row r="461" ht="14" customHeight="1">
+      <c r="A461" s="16" t="n"/>
+      <c r="B461" s="16" t="n"/>
+    </row>
+    <row r="462" ht="14" customHeight="1">
+      <c r="A462" s="16" t="n"/>
+      <c r="B462" s="16" t="n"/>
+    </row>
+    <row r="463" ht="14" customHeight="1">
+      <c r="A463" s="16" t="n"/>
+      <c r="B463" s="16" t="n"/>
+    </row>
+    <row r="464" ht="14" customHeight="1">
+      <c r="A464" s="16" t="n"/>
+      <c r="B464" s="16" t="n"/>
+    </row>
+    <row r="465" ht="14" customHeight="1">
+      <c r="A465" s="16" t="n"/>
+      <c r="B465" s="16" t="n"/>
+    </row>
+    <row r="466" ht="14" customHeight="1">
+      <c r="A466" s="16" t="n"/>
+      <c r="B466" s="16" t="n"/>
+    </row>
+    <row r="467" ht="10" customHeight="1"/>
+    <row r="468" ht="10" customHeight="1"/>
+    <row r="469" ht="30" customHeight="1">
+      <c r="A469" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-016</t>
+        </is>
+      </c>
+      <c r="B469" s="15" t="inlineStr">
+        <is>
+          <t>GET /api/users (admin=role_id:1) → A001ユーザー一覧2件返却確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="14" customHeight="1">
+      <c r="A470" s="16" t="n"/>
+      <c r="B470" s="16" t="n"/>
+    </row>
+    <row r="471" ht="14" customHeight="1">
+      <c r="A471" s="16" t="n"/>
+      <c r="B471" s="16" t="n"/>
+    </row>
+    <row r="472" ht="14" customHeight="1">
+      <c r="A472" s="16" t="n"/>
+      <c r="B472" s="16" t="n"/>
+    </row>
+    <row r="473" ht="14" customHeight="1">
+      <c r="A473" s="16" t="n"/>
+      <c r="B473" s="16" t="n"/>
+    </row>
+    <row r="474" ht="14" customHeight="1">
+      <c r="A474" s="16" t="n"/>
+      <c r="B474" s="16" t="n"/>
+    </row>
+    <row r="475" ht="14" customHeight="1">
+      <c r="A475" s="16" t="n"/>
+      <c r="B475" s="16" t="n"/>
+    </row>
+    <row r="476" ht="14" customHeight="1">
+      <c r="A476" s="16" t="n"/>
+      <c r="B476" s="16" t="n"/>
+    </row>
+    <row r="477" ht="14" customHeight="1">
+      <c r="A477" s="16" t="n"/>
+      <c r="B477" s="16" t="n"/>
+    </row>
+    <row r="478" ht="14" customHeight="1">
+      <c r="A478" s="16" t="n"/>
+      <c r="B478" s="16" t="n"/>
+    </row>
+    <row r="479" ht="14" customHeight="1">
+      <c r="A479" s="16" t="n"/>
+      <c r="B479" s="16" t="n"/>
+    </row>
+    <row r="480" ht="14" customHeight="1">
+      <c r="A480" s="16" t="n"/>
+      <c r="B480" s="16" t="n"/>
+    </row>
+    <row r="481" ht="14" customHeight="1">
+      <c r="A481" s="16" t="n"/>
+      <c r="B481" s="16" t="n"/>
+    </row>
+    <row r="482" ht="14" customHeight="1">
+      <c r="A482" s="16" t="n"/>
+      <c r="B482" s="16" t="n"/>
+    </row>
+    <row r="483" ht="14" customHeight="1">
+      <c r="A483" s="16" t="n"/>
+      <c r="B483" s="16" t="n"/>
+    </row>
+    <row r="484" ht="14" customHeight="1">
+      <c r="A484" s="16" t="n"/>
+      <c r="B484" s="16" t="n"/>
+    </row>
+    <row r="485" ht="14" customHeight="1">
+      <c r="A485" s="16" t="n"/>
+      <c r="B485" s="16" t="n"/>
+    </row>
+    <row r="486" ht="14" customHeight="1">
+      <c r="A486" s="16" t="n"/>
+      <c r="B486" s="16" t="n"/>
+    </row>
+    <row r="487" ht="14" customHeight="1">
+      <c r="A487" s="16" t="n"/>
+      <c r="B487" s="16" t="n"/>
+    </row>
+    <row r="488" ht="14" customHeight="1">
+      <c r="A488" s="16" t="n"/>
+      <c r="B488" s="16" t="n"/>
+    </row>
+    <row r="489" ht="14" customHeight="1">
+      <c r="A489" s="16" t="n"/>
+      <c r="B489" s="16" t="n"/>
+    </row>
+    <row r="490" ht="14" customHeight="1">
+      <c r="A490" s="16" t="n"/>
+      <c r="B490" s="16" t="n"/>
+    </row>
+    <row r="491" ht="14" customHeight="1">
+      <c r="A491" s="16" t="n"/>
+      <c r="B491" s="16" t="n"/>
+    </row>
+    <row r="492" ht="14" customHeight="1">
+      <c r="A492" s="16" t="n"/>
+      <c r="B492" s="16" t="n"/>
+    </row>
+    <row r="493" ht="14" customHeight="1">
+      <c r="A493" s="16" t="n"/>
+      <c r="B493" s="16" t="n"/>
+    </row>
+    <row r="494" ht="14" customHeight="1">
+      <c r="A494" s="16" t="n"/>
+      <c r="B494" s="16" t="n"/>
+    </row>
+    <row r="495" ht="14" customHeight="1">
+      <c r="A495" s="16" t="n"/>
+      <c r="B495" s="16" t="n"/>
+    </row>
+    <row r="496" ht="14" customHeight="1">
+      <c r="A496" s="16" t="n"/>
+      <c r="B496" s="16" t="n"/>
+    </row>
+    <row r="497" ht="14" customHeight="1">
+      <c r="A497" s="16" t="n"/>
+      <c r="B497" s="16" t="n"/>
+    </row>
+    <row r="498" ht="10" customHeight="1"/>
+    <row r="499" ht="10" customHeight="1"/>
+    <row r="500" ht="30" customHeight="1">
+      <c r="A500" s="14" t="inlineStr">
+        <is>
+          <t>UT-AUTH-017</t>
+        </is>
+      </c>
+      <c r="B500" s="15" t="inlineStr">
+        <is>
+          <t>staff1 で admin.html 直接アクセス → dashboard.html リダイレクト確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="14" customHeight="1">
+      <c r="A501" s="16" t="n"/>
+      <c r="B501" s="16" t="n"/>
+    </row>
+    <row r="502" ht="14" customHeight="1">
+      <c r="A502" s="16" t="n"/>
+      <c r="B502" s="16" t="n"/>
+    </row>
+    <row r="503" ht="14" customHeight="1">
+      <c r="A503" s="16" t="n"/>
+      <c r="B503" s="16" t="n"/>
+    </row>
+    <row r="504" ht="14" customHeight="1">
+      <c r="A504" s="16" t="n"/>
+      <c r="B504" s="16" t="n"/>
+    </row>
+    <row r="505" ht="14" customHeight="1">
+      <c r="A505" s="16" t="n"/>
+      <c r="B505" s="16" t="n"/>
+    </row>
+    <row r="506" ht="14" customHeight="1">
+      <c r="A506" s="16" t="n"/>
+      <c r="B506" s="16" t="n"/>
+    </row>
+    <row r="507" ht="14" customHeight="1">
+      <c r="A507" s="16" t="n"/>
+      <c r="B507" s="16" t="n"/>
+    </row>
+    <row r="508" ht="14" customHeight="1">
+      <c r="A508" s="16" t="n"/>
+      <c r="B508" s="16" t="n"/>
+    </row>
+    <row r="509" ht="14" customHeight="1">
+      <c r="A509" s="16" t="n"/>
+      <c r="B509" s="16" t="n"/>
+    </row>
+    <row r="510" ht="14" customHeight="1">
+      <c r="A510" s="16" t="n"/>
+      <c r="B510" s="16" t="n"/>
+    </row>
+    <row r="511" ht="14" customHeight="1">
+      <c r="A511" s="16" t="n"/>
+      <c r="B511" s="16" t="n"/>
+    </row>
+    <row r="512" ht="14" customHeight="1">
+      <c r="A512" s="16" t="n"/>
+      <c r="B512" s="16" t="n"/>
+    </row>
+    <row r="513" ht="14" customHeight="1">
+      <c r="A513" s="16" t="n"/>
+      <c r="B513" s="16" t="n"/>
+    </row>
+    <row r="514" ht="14" customHeight="1">
+      <c r="A514" s="16" t="n"/>
+      <c r="B514" s="16" t="n"/>
+    </row>
+    <row r="515" ht="14" customHeight="1">
+      <c r="A515" s="16" t="n"/>
+      <c r="B515" s="16" t="n"/>
+    </row>
+    <row r="516" ht="14" customHeight="1">
+      <c r="A516" s="16" t="n"/>
+      <c r="B516" s="16" t="n"/>
+    </row>
+    <row r="517" ht="14" customHeight="1">
+      <c r="A517" s="16" t="n"/>
+      <c r="B517" s="16" t="n"/>
+    </row>
+    <row r="518" ht="14" customHeight="1">
+      <c r="A518" s="16" t="n"/>
+      <c r="B518" s="16" t="n"/>
+    </row>
+    <row r="519" ht="14" customHeight="1">
+      <c r="A519" s="16" t="n"/>
+      <c r="B519" s="16" t="n"/>
+    </row>
+    <row r="520" ht="14" customHeight="1">
+      <c r="A520" s="16" t="n"/>
+      <c r="B520" s="16" t="n"/>
+    </row>
+    <row r="521" ht="14" customHeight="1">
+      <c r="A521" s="16" t="n"/>
+      <c r="B521" s="16" t="n"/>
+    </row>
+    <row r="522" ht="14" customHeight="1">
+      <c r="A522" s="16" t="n"/>
+      <c r="B522" s="16" t="n"/>
+    </row>
+    <row r="523" ht="14" customHeight="1">
+      <c r="A523" s="16" t="n"/>
+      <c r="B523" s="16" t="n"/>
+    </row>
+    <row r="524" ht="14" customHeight="1">
+      <c r="A524" s="16" t="n"/>
+      <c r="B524" s="16" t="n"/>
+    </row>
+    <row r="525" ht="14" customHeight="1">
+      <c r="A525" s="16" t="n"/>
+      <c r="B525" s="16" t="n"/>
+    </row>
+    <row r="526" ht="14" customHeight="1">
+      <c r="A526" s="16" t="n"/>
+      <c r="B526" s="16" t="n"/>
+    </row>
+    <row r="527" ht="14" customHeight="1">
+      <c r="A527" s="16" t="n"/>
+      <c r="B527" s="16" t="n"/>
+    </row>
+    <row r="528" ht="14" customHeight="1">
+      <c r="A528" s="16" t="n"/>
+      <c r="B528" s="16" t="n"/>
+    </row>
+    <row r="529" ht="10" customHeight="1"/>
+    <row r="530" ht="10" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>